--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -11316,10 +11316,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669908</v>
+        <v>119669907</v>
       </c>
       <c r="B101" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11328,43 +11328,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>749547</v>
+        <v>749493</v>
       </c>
       <c r="R101" t="n">
-        <v>7089069</v>
+        <v>7088992</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11420,12 +11415,12 @@
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>Äldre gran</t>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre gran</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11443,10 +11438,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119669907</v>
+        <v>119669908</v>
       </c>
       <c r="B102" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,38 +11450,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>749493</v>
+        <v>749547</v>
       </c>
       <c r="R102" t="n">
-        <v>7088992</v>
+        <v>7089069</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11542,12 +11542,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>Stående, död</t>
+          <t>Äldre gran</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies # Äldre gran</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>

--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -11316,10 +11316,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669907</v>
+        <v>119669908</v>
       </c>
       <c r="B101" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11328,38 +11328,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>749493</v>
+        <v>749547</v>
       </c>
       <c r="R101" t="n">
-        <v>7088992</v>
+        <v>7089069</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11415,12 +11420,12 @@
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>Stående, död</t>
+          <t>Äldre gran</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies # Äldre gran</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11438,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119669908</v>
+        <v>119669907</v>
       </c>
       <c r="B102" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11450,43 +11455,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>749547</v>
+        <v>749493</v>
       </c>
       <c r="R102" t="n">
-        <v>7089069</v>
+        <v>7088992</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11542,12 +11542,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>Äldre gran</t>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre gran</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>

--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -10721,10 +10721,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119669906</v>
+        <v>119669923</v>
       </c>
       <c r="B96" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10733,38 +10733,47 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>749389</v>
+        <v>749515</v>
       </c>
       <c r="R96" t="n">
-        <v>7089021</v>
+        <v>7088979</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10799,39 +10808,15 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Plockepinn av granlågor</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -10848,7 +10833,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119669909</v>
+        <v>119669908</v>
       </c>
       <c r="B97" t="n">
         <v>57310</v>
@@ -10884,7 +10869,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10893,10 +10878,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>749503</v>
+        <v>749547</v>
       </c>
       <c r="R97" t="n">
-        <v>7088993</v>
+        <v>7089069</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10931,11 +10916,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10955,9 +10935,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Äldre gran</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Äldre gran</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -10975,7 +10960,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119669917</v>
+        <v>119669916</v>
       </c>
       <c r="B98" t="n">
         <v>57326</v>
@@ -11011,7 +10996,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11020,10 +11005,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>749490</v>
+        <v>749500</v>
       </c>
       <c r="R98" t="n">
-        <v>7088980</v>
+        <v>7089085</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11069,22 +11054,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11102,10 +11082,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119669921</v>
+        <v>119669917</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11118,34 +11098,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>749536</v>
+        <v>749490</v>
       </c>
       <c r="R99" t="n">
-        <v>7089106</v>
+        <v>7088980</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11188,6 +11173,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11204,10 +11209,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119669923</v>
+        <v>119669906</v>
       </c>
       <c r="B100" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11216,47 +11221,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>749515</v>
+        <v>749389</v>
       </c>
       <c r="R100" t="n">
-        <v>7088979</v>
+        <v>7089021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,15 +11287,39 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Plockepinn av granlågor</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11316,7 +11336,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669908</v>
+        <v>119669909</v>
       </c>
       <c r="B101" t="n">
         <v>57310</v>
@@ -11352,7 +11372,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11361,10 +11381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>749547</v>
+        <v>749503</v>
       </c>
       <c r="R101" t="n">
-        <v>7089069</v>
+        <v>7088993</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11399,6 +11419,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11418,14 +11443,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Äldre gran</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11443,10 +11463,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119669907</v>
+        <v>119669921</v>
       </c>
       <c r="B102" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,25 +11475,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11483,10 +11503,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>749493</v>
+        <v>749536</v>
       </c>
       <c r="R102" t="n">
-        <v>7088992</v>
+        <v>7089106</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11529,26 +11549,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående, död</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119669916</v>
+        <v>119669907</v>
       </c>
       <c r="B104" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11698,43 +11698,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>749500</v>
+        <v>749493</v>
       </c>
       <c r="R104" t="n">
-        <v>7089085</v>
+        <v>7088992</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11780,17 +11775,22 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>

--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -10721,10 +10721,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119669923</v>
+        <v>119669916</v>
       </c>
       <c r="B96" t="n">
-        <v>5169</v>
+        <v>57326</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10733,47 +10733,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>749515</v>
+        <v>749500</v>
       </c>
       <c r="R96" t="n">
-        <v>7088979</v>
+        <v>7089085</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10814,9 +10810,23 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -10833,10 +10843,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119669908</v>
+        <v>119669917</v>
       </c>
       <c r="B97" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10849,16 +10859,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10869,7 +10879,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10878,10 +10888,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>749547</v>
+        <v>749490</v>
       </c>
       <c r="R97" t="n">
-        <v>7089069</v>
+        <v>7088980</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10937,12 +10947,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Äldre gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre gran</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -10960,10 +10970,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119669916</v>
+        <v>119669923</v>
       </c>
       <c r="B98" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10972,43 +10982,47 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>749500</v>
+        <v>749515</v>
       </c>
       <c r="R98" t="n">
-        <v>7089085</v>
+        <v>7088979</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11049,23 +11063,9 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11082,10 +11082,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119669917</v>
+        <v>119669921</v>
       </c>
       <c r="B99" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11098,39 +11098,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>749490</v>
+        <v>749536</v>
       </c>
       <c r="R99" t="n">
-        <v>7088980</v>
+        <v>7089106</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11173,26 +11168,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11336,10 +11311,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669909</v>
+        <v>119669919</v>
       </c>
       <c r="B101" t="n">
-        <v>57310</v>
+        <v>90954</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11352,39 +11327,32 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>749503</v>
+        <v>749552</v>
       </c>
       <c r="R101" t="n">
-        <v>7088993</v>
+        <v>7089076</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11419,17 +11387,13 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11443,9 +11407,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11463,10 +11432,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119669921</v>
+        <v>119669907</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11475,25 +11444,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11503,10 +11472,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>749536</v>
+        <v>749493</v>
       </c>
       <c r="R102" t="n">
-        <v>7089106</v>
+        <v>7088992</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11549,6 +11518,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående, död</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11565,10 +11554,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119669919</v>
+        <v>119669909</v>
       </c>
       <c r="B103" t="n">
-        <v>90954</v>
+        <v>57310</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11581,32 +11570,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>749552</v>
+        <v>749503</v>
       </c>
       <c r="R103" t="n">
-        <v>7089076</v>
+        <v>7088993</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11641,13 +11637,17 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11661,14 +11661,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11686,10 +11681,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119669907</v>
+        <v>119669908</v>
       </c>
       <c r="B104" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11698,38 +11693,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>749493</v>
+        <v>749547</v>
       </c>
       <c r="R104" t="n">
-        <v>7088992</v>
+        <v>7089069</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>Stående, död</t>
+          <t>Äldre gran</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies # Äldre gran</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>

--- a/artfynd/A 44724-2023 artfynd.xlsx
+++ b/artfynd/A 44724-2023 artfynd.xlsx
@@ -10721,7 +10721,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119669916</v>
+        <v>119669917</v>
       </c>
       <c r="B96" t="n">
         <v>57326</v>
@@ -10757,7 +10757,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10766,10 +10766,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>749500</v>
+        <v>749490</v>
       </c>
       <c r="R96" t="n">
-        <v>7089085</v>
+        <v>7088980</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10815,17 +10815,22 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -10843,10 +10848,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119669917</v>
+        <v>119669921</v>
       </c>
       <c r="B97" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10859,39 +10864,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>749490</v>
+        <v>749536</v>
       </c>
       <c r="R97" t="n">
-        <v>7088980</v>
+        <v>7089106</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10934,26 +10934,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10970,10 +10950,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119669923</v>
+        <v>119669906</v>
       </c>
       <c r="B98" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10982,47 +10962,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>749515</v>
+        <v>749389</v>
       </c>
       <c r="R98" t="n">
-        <v>7088979</v>
+        <v>7089021</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11057,15 +11028,39 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Plockepinn av granlågor</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11082,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119669921</v>
+        <v>119669919</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>90954</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11098,34 +11093,32 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>749536</v>
+        <v>749552</v>
       </c>
       <c r="R99" t="n">
-        <v>7089106</v>
+        <v>7089076</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11166,8 +11159,29 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11184,10 +11198,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119669906</v>
+        <v>119669907</v>
       </c>
       <c r="B100" t="n">
-        <v>90562</v>
+        <v>91254</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11196,25 +11210,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11224,10 +11238,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>749389</v>
+        <v>749493</v>
       </c>
       <c r="R100" t="n">
-        <v>7089021</v>
+        <v>7088992</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11262,11 +11276,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Plockepinn av granlågor</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11288,12 +11297,12 @@
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11311,10 +11320,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669919</v>
+        <v>119669908</v>
       </c>
       <c r="B101" t="n">
-        <v>90954</v>
+        <v>57310</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11327,32 +11336,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>749552</v>
+        <v>749547</v>
       </c>
       <c r="R101" t="n">
-        <v>7089076</v>
+        <v>7089069</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11393,7 +11409,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11409,12 +11424,12 @@
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre gran</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Äldre gran</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11432,10 +11447,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119669907</v>
+        <v>119669909</v>
       </c>
       <c r="B102" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11444,38 +11459,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>749493</v>
+        <v>749503</v>
       </c>
       <c r="R102" t="n">
-        <v>7088992</v>
+        <v>7088993</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,6 +11530,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11529,14 +11554,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11554,10 +11574,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119669909</v>
+        <v>119669916</v>
       </c>
       <c r="B103" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11570,16 +11590,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11590,7 +11610,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11599,10 +11619,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>749503</v>
+        <v>749500</v>
       </c>
       <c r="R103" t="n">
-        <v>7088993</v>
+        <v>7089085</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11637,11 +11657,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11653,17 +11668,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11681,10 +11696,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119669908</v>
+        <v>119669923</v>
       </c>
       <c r="B104" t="n">
-        <v>57310</v>
+        <v>5169</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11693,43 +11708,47 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Klabberget, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>749547</v>
+        <v>749515</v>
       </c>
       <c r="R104" t="n">
-        <v>7089069</v>
+        <v>7088979</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11770,28 +11789,9 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>Äldre gran</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre gran</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
